--- a/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -573,7 +573,7 @@
 https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-observation</t>
   </si>
   <si>
-    <t>Observations associées et rattachées à cette entree</t>
+    <t>Observations associées</t>
   </si>
 </sst>
 </file>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-history.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="181">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -472,6 +472,9 @@
   </si>
   <si>
     <t>Type d'observation</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>jdv-historique-grossesses-cisis (1.2.250.1.213.1.1.5.852)</t>
@@ -3086,13 +3089,13 @@
         <v>73</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
@@ -3127,10 +3130,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3156,10 +3159,10 @@
         <v>131</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3210,7 +3213,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3227,10 +3230,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3256,10 +3259,10 @@
         <v>80</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3310,7 +3313,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3327,10 +3330,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3353,13 +3356,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3410,7 +3413,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3427,10 +3430,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3456,10 +3459,10 @@
         <v>80</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3510,7 +3513,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3527,10 +3530,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3553,13 +3556,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3610,7 +3613,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -3627,10 +3630,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3653,13 +3656,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3710,7 +3713,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3727,10 +3730,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3756,10 +3759,10 @@
         <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3810,7 +3813,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3827,10 +3830,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3856,10 +3859,10 @@
         <v>131</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3910,7 +3913,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3927,10 +3930,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3953,13 +3956,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4010,7 +4013,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4027,10 +4030,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4056,10 +4059,10 @@
         <v>80</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4110,7 +4113,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4127,10 +4130,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4153,13 +4156,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4210,7 +4213,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4227,10 +4230,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4253,13 +4256,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4310,7 +4313,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
